--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.99681</v>
+        <v>18.02503</v>
       </c>
       <c r="D2" t="n">
-        <v>17.57517</v>
+        <v>17.43525</v>
       </c>
       <c r="E2" t="n">
-        <v>17.68171</v>
+        <v>17.67404</v>
       </c>
       <c r="F2" t="n">
-        <v>44.47954</v>
+        <v>45.49182</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05436</v>
+        <v>0.05424</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91428</v>
+        <v>1.91757</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.52707</v>
+        <v>17.59887</v>
       </c>
       <c r="D3" t="n">
-        <v>17.81584</v>
+        <v>17.34664</v>
       </c>
       <c r="E3" t="n">
-        <v>17.2201</v>
+        <v>17.55518</v>
       </c>
       <c r="F3" t="n">
-        <v>45.58006</v>
+        <v>45.66195</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05349</v>
+        <v>0.05446</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90999</v>
+        <v>1.9218</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.92507</v>
+        <v>17.90211</v>
       </c>
       <c r="D4" t="n">
-        <v>17.26974</v>
+        <v>17.5319</v>
       </c>
       <c r="E4" t="n">
-        <v>17.98286</v>
+        <v>17.73262</v>
       </c>
       <c r="F4" t="n">
-        <v>44.81168</v>
+        <v>45.03461</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05391</v>
+        <v>0.05377</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9429</v>
+        <v>1.92816</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.79921</v>
+        <v>17.74678</v>
       </c>
       <c r="D6" t="n">
-        <v>16.84708</v>
+        <v>17.01202</v>
       </c>
       <c r="E6" t="n">
-        <v>17.55693</v>
+        <v>17.31024</v>
       </c>
       <c r="F6" t="n">
-        <v>23.23732</v>
+        <v>23.42328</v>
       </c>
       <c r="G6" t="n">
-        <v>35.77161</v>
+        <v>35.89169</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.62579</v>
+        <v>17.56534</v>
       </c>
       <c r="D7" t="n">
-        <v>16.72649</v>
+        <v>16.99865</v>
       </c>
       <c r="E7" t="n">
-        <v>17.52207</v>
+        <v>17.24499</v>
       </c>
       <c r="F7" t="n">
-        <v>23.07488</v>
+        <v>23.31722</v>
       </c>
       <c r="G7" t="n">
-        <v>36.68097</v>
+        <v>35.86356</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.74452</v>
+        <v>17.30455</v>
       </c>
       <c r="D8" t="n">
-        <v>16.51881</v>
+        <v>16.98464</v>
       </c>
       <c r="E8" t="n">
-        <v>17.17335</v>
+        <v>17.27583</v>
       </c>
       <c r="F8" t="n">
-        <v>22.63362</v>
+        <v>22.98108</v>
       </c>
       <c r="G8" t="n">
-        <v>36.54182</v>
+        <v>36.55194</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.63683</v>
+        <v>0.65306</v>
       </c>
       <c r="D10" t="n">
-        <v>1.19019</v>
+        <v>1.16391</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6424800000000001</v>
+        <v>0.64577</v>
       </c>
       <c r="D11" t="n">
-        <v>1.19138</v>
+        <v>1.16886</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6476</v>
+        <v>0.64342</v>
       </c>
       <c r="D12" t="n">
-        <v>1.17643</v>
+        <v>1.20432</v>
       </c>
     </row>
   </sheetData>
